--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,36 +446,42 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Account.extension:AnzahlVerlegungen</t>
+    <t>Account.extension:anzahlVerlegungen</t>
+  </si>
+  <si>
+    <t>anzahlVerlegungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-anzahlVerlegungen}
+</t>
   </si>
   <si>
     <t>AnzahlVerlegungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AnzahlVerlegungen}
+    <t>MOPED Extension für die Anzahl der Verlegungen</t>
+  </si>
+  <si>
+    <t>Account.extension:anzahlBeurlaubungen</t>
+  </si>
+  <si>
+    <t>anzahlBeurlaubungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-anzahlBeurlaubungen}
 </t>
   </si>
   <si>
-    <t>MOPED Extension für die Anzahl der Verlegungen</t>
-  </si>
-  <si>
-    <t>Account.extension:AnzahlBeurlaubungen</t>
-  </si>
-  <si>
     <t>AnzahlBeurlaubungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AnzahlBeurlaubungen}
-</t>
-  </si>
-  <si>
     <t>MOPED Extension für die Anzahl der Beurlaubungen</t>
   </si>
   <si>
-    <t>Account.extension:VDASID</t>
-  </si>
-  <si>
-    <t>VDASID</t>
+    <t>Account.extension:vdasid</t>
+  </si>
+  <si>
+    <t>vdasid</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vdasid}
@@ -490,13 +496,13 @@
 Um eine zwischenstaatliche Verrechnung zu ermöglichen ist bei zwischenstaatlichen Fällen eine Ablehnung zulässig.</t>
   </si>
   <si>
-    <t>Account.extension:WorkflowStatus</t>
-  </si>
-  <si>
-    <t>WorkflowStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-workflow-status}
+    <t>Account.extension:workflowStatus</t>
+  </si>
+  <si>
+    <t>workflowStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-workflowStatus}
 </t>
   </si>
   <si>
@@ -506,13 +512,13 @@
     <t>MOPED Extension für den Workflowstatus. Dieser beschreibt den Zustand in dem sich der administrative Fall derzeit befindet</t>
   </si>
   <si>
-    <t>Account.extension:VerdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t>VerdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-VerdachtArbeitsSchuelerunfall}
+    <t>Account.extension:verdachtArbeitsSchuelerunfall</t>
+  </si>
+  <si>
+    <t>verdachtArbeitsSchuelerunfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verdachtArbeitsSchuelerunfall}
 </t>
   </si>
   <si>
@@ -522,13 +528,13 @@
     <t>MOPED Extension für den Verdacht auf einen Arbeits- oder Schuelerunfall.</t>
   </si>
   <si>
-    <t>Account.extension:VerdachtFremdverschulden</t>
-  </si>
-  <si>
-    <t>VerdachtFremdverschulden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-VerdachtFremdverschulden}
+    <t>Account.extension:verdachtFremdverschulden</t>
+  </si>
+  <si>
+    <t>verdachtFremdverschulden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verdachtFremdverschulden}
 </t>
   </si>
   <si>
@@ -538,13 +544,13 @@
     <t>MOPED Extension für den Verdacht auf Fremdverschulden</t>
   </si>
   <si>
-    <t>Account.extension:TageOhneKostenbeitrag</t>
-  </si>
-  <si>
-    <t>TageOhneKostenbeitrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-TageOhneKostenbeitrag}
+    <t>Account.extension:tageOhneKostenbeitrag</t>
+  </si>
+  <si>
+    <t>tageOhneKostenbeitrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-tageOhneKostenbeitrag}
 </t>
   </si>
   <si>
@@ -554,13 +560,13 @@
     <t>Anzahl der Tage, für welche kein Kostenbeitrag seitens der Krankenanstalt eingehoben wurde</t>
   </si>
   <si>
-    <t>Account.extension:CoverageEligibilityRequestRef</t>
-  </si>
-  <si>
-    <t>CoverageEligibilityRequestRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-CoverageEligibilityRequestRef}
+    <t>Account.extension:coverageEligibilityRequestRef</t>
+  </si>
+  <si>
+    <t>coverageEligibilityRequestRef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-coverageEligibilityRequestRef}
 </t>
   </si>
   <si>
@@ -570,13 +576,13 @@
     <t>Referenz vom Account auf den CoverageEligibilityRequest.</t>
   </si>
   <si>
-    <t>Account.extension:ClaimRef</t>
-  </si>
-  <si>
-    <t>ClaimRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-ClaimRef}
+    <t>Account.extension:claimRef</t>
+  </si>
+  <si>
+    <t>claimRef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-claimRef}
 </t>
   </si>
   <si>
@@ -1613,9 +1619,9 @@
   <dimension ref="A1:AL77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.5703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.40234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.22265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1623,7 +1629,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.33984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2657,10 +2663,10 @@
         <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2734,13 +2740,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>19</v>
@@ -2762,13 +2768,13 @@
         <v>19</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2842,13 +2848,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>19</v>
@@ -2870,13 +2876,13 @@
         <v>19</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2950,13 +2956,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>19</v>
@@ -2978,13 +2984,13 @@
         <v>19</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3058,13 +3064,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>19</v>
@@ -3086,13 +3092,13 @@
         <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3166,13 +3172,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>19</v>
@@ -3194,13 +3200,13 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3274,13 +3280,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>19</v>
@@ -3302,13 +3308,13 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3382,13 +3388,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>19</v>
@@ -3410,13 +3416,13 @@
         <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3490,13 +3496,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>19</v>
@@ -3518,13 +3524,13 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3598,14 +3604,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3627,16 +3633,16 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -3685,7 +3691,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3708,10 +3714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3734,13 +3740,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3791,7 +3797,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3806,18 +3812,18 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3843,13 +3849,13 @@
         <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3878,10 +3884,10 @@
         <v>108</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -3899,7 +3905,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -3914,18 +3920,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3948,13 +3954,13 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3981,13 +3987,13 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -4005,7 +4011,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4028,10 +4034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4054,13 +4060,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4087,13 +4093,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4111,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4126,22 +4132,22 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4160,13 +4166,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4217,7 +4223,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4232,22 +4238,22 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4266,16 +4272,16 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4325,7 +4331,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4340,18 +4346,18 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4374,16 +4380,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4433,7 +4439,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4448,18 +4454,18 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4482,16 +4488,16 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4541,7 +4547,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4559,15 +4565,15 @@
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4590,13 +4596,13 @@
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4647,7 +4653,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4656,7 +4662,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>19</v>
@@ -4665,19 +4671,19 @@
         <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4699,13 +4705,13 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4755,7 +4761,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4773,19 +4779,19 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4807,16 +4813,16 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -4865,7 +4871,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4888,10 +4894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4914,13 +4920,13 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4971,7 +4977,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>84</v>
@@ -4989,19 +4995,19 @@
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5020,16 +5026,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5079,7 +5085,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5097,15 +5103,15 @@
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5128,13 +5134,13 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5185,7 +5191,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5203,15 +5209,15 @@
         <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5234,13 +5240,13 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5291,7 +5297,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5309,15 +5315,15 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5340,13 +5346,13 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5397,7 +5403,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5415,15 +5421,15 @@
         <v>19</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5446,13 +5452,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5503,7 +5509,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5512,7 +5518,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>19</v>
@@ -5521,19 +5527,19 @@
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5555,13 +5561,13 @@
         <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5611,7 +5617,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5629,19 +5635,19 @@
         <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5663,16 +5669,16 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -5721,7 +5727,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5744,10 +5750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5770,13 +5776,13 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5827,7 +5833,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -5845,15 +5851,15 @@
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5876,13 +5882,13 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5933,7 +5939,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5951,15 +5957,15 @@
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5982,13 +5988,13 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6039,7 +6045,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6057,15 +6063,15 @@
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6088,13 +6094,13 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6145,7 +6151,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6157,7 +6163,7 @@
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>19</v>
@@ -6168,10 +6174,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6194,13 +6200,13 @@
         <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6251,7 +6257,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6260,7 +6266,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>19</v>
@@ -6269,19 +6275,19 @@
         <v>19</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6303,13 +6309,13 @@
         <v>131</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6359,7 +6365,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6377,19 +6383,19 @@
         <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6411,16 +6417,16 @@
         <v>131</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -6469,7 +6475,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6492,10 +6498,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6518,13 +6524,13 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6575,7 +6581,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6598,14 +6604,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6624,13 +6630,13 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6657,11 +6663,11 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -6679,7 +6685,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -6688,7 +6694,7 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>96</v>
@@ -6702,10 +6708,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6728,13 +6734,13 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6785,7 +6791,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6794,7 +6800,7 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>96</v>
@@ -6808,10 +6814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6834,13 +6840,13 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6867,13 +6873,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -6891,7 +6897,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -6914,10 +6920,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6940,13 +6946,13 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6997,7 +7003,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7020,10 +7026,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7046,13 +7052,13 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7079,10 +7085,10 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>19</v>
@@ -7103,7 +7109,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7126,10 +7132,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7152,13 +7158,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7209,7 +7215,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7221,7 +7227,7 @@
         <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>19</v>
@@ -7232,10 +7238,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7258,13 +7264,13 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7315,7 +7321,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7324,7 +7330,7 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>19</v>
@@ -7333,19 +7339,19 @@
         <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7367,13 +7373,13 @@
         <v>131</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7423,7 +7429,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7441,19 +7447,19 @@
         <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7475,16 +7481,16 @@
         <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -7533,7 +7539,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7556,10 +7562,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7582,13 +7588,13 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7639,7 +7645,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7662,14 +7668,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7688,13 +7694,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7721,11 +7727,11 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -7743,7 +7749,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -7752,7 +7758,7 @@
         <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>96</v>
@@ -7766,10 +7772,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7792,13 +7798,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7849,7 +7855,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -7858,7 +7864,7 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>96</v>
@@ -7872,10 +7878,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7898,13 +7904,13 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7931,10 +7937,10 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>19</v>
@@ -7955,7 +7961,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7978,10 +7984,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8004,13 +8010,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8037,10 +8043,10 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>19</v>
@@ -8061,7 +8067,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8084,10 +8090,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8110,13 +8116,13 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8167,7 +8173,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8190,10 +8196,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8216,13 +8222,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8273,7 +8279,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -8296,10 +8302,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8322,13 +8328,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8379,7 +8385,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8388,7 +8394,7 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>19</v>
@@ -8397,19 +8403,19 @@
         <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8431,13 +8437,13 @@
         <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8487,7 +8493,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8505,19 +8511,19 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8539,16 +8545,16 @@
         <v>131</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -8597,7 +8603,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8620,10 +8626,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8646,13 +8652,13 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8679,13 +8685,13 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -8703,7 +8709,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8726,10 +8732,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8752,13 +8758,13 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8809,7 +8815,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8832,10 +8838,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8858,13 +8864,13 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8895,7 +8901,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -8913,7 +8919,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -8936,10 +8942,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8962,13 +8968,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9019,7 +9025,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9042,10 +9048,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9068,13 +9074,13 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9125,7 +9131,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9134,7 +9140,7 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>19</v>
@@ -9143,19 +9149,19 @@
         <v>19</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9177,13 +9183,13 @@
         <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9233,7 +9239,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9251,19 +9257,19 @@
         <v>19</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9285,16 +9291,16 @@
         <v>131</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -9343,7 +9349,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9366,10 +9372,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9392,13 +9398,13 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9425,13 +9431,13 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -9449,7 +9455,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9472,10 +9478,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9498,13 +9504,13 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9531,13 +9537,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -9555,7 +9561,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -9578,10 +9584,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9604,13 +9610,13 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9661,7 +9667,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -9684,10 +9690,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9710,13 +9716,13 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9767,7 +9773,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -9790,10 +9796,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9816,16 +9822,16 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9875,7 +9881,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
